--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/дв 29,06,26 днрсч ост ки от Титенко.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/дв 29,06,26 днрсч ост ки от Титенко.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE6AB0C-A6B2-4102-8448-BBFD31213C74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA9EA0A-3D83-4A12-B141-46B0D9F9FF3D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1318,15 +1318,15 @@
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>17983</v>
+        <v>17793</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>9749</v>
+        <v>9647</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" ref="U5" si="1">SUM(U6:U499)</f>
-        <v>8234</v>
+        <v>8146</v>
       </c>
       <c r="V5" s="4">
         <f t="shared" si="0"/>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="W6" s="1"/>
       <c r="X6" s="1">
-        <f>(F6+O6+P6+S6)/Q6</f>
+        <f t="shared" ref="X6:X37" si="4">(F6+O6+P6+S6)/Q6</f>
         <v>15.1</v>
       </c>
       <c r="Y6" s="1">
-        <f t="shared" ref="Y6:Y37" si="4">(F6+O6+P6)/Q6</f>
+        <f t="shared" ref="Y6:Y37" si="5">(F6+O6+P6)/Q6</f>
         <v>14.1</v>
       </c>
       <c r="Z6" s="1">
@@ -1554,7 +1554,7 @@
         <v>10</v>
       </c>
       <c r="T7" s="5">
-        <f t="shared" ref="T7:T70" si="5">ROUND(S7-U7,0)</f>
+        <f t="shared" ref="T7:T70" si="6">ROUND(S7-U7,0)</f>
         <v>10</v>
       </c>
       <c r="U7" s="5"/>
@@ -1563,11 +1563,11 @@
       </c>
       <c r="W7" s="1"/>
       <c r="X7" s="1">
-        <f>(F7+O7+P7+S7)/Q7</f>
+        <f t="shared" si="4"/>
         <v>30.322259136212622</v>
       </c>
       <c r="Y7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22.016611295681063</v>
       </c>
       <c r="Z7" s="1">
@@ -1587,11 +1587,11 @@
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1">
-        <f t="shared" ref="AF7:AF70" si="6">G7*T7</f>
+        <f t="shared" ref="AF7:AF70" si="7">G7*T7</f>
         <v>10</v>
       </c>
       <c r="AG7" s="1">
-        <f t="shared" ref="AG7:AG70" si="7">G7*U7</f>
+        <f t="shared" ref="AG7:AG70" si="8">G7*U7</f>
         <v>0</v>
       </c>
       <c r="AH7" s="1"/>
@@ -1665,24 +1665,24 @@
       </c>
       <c r="R8" s="5"/>
       <c r="S8" s="5">
-        <f t="shared" ref="S8:S70" si="8">ROUND(R8,0)</f>
+        <f t="shared" ref="S8:S70" si="9">ROUND(R8,0)</f>
         <v>0</v>
       </c>
       <c r="T8" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1">
-        <f>(F8+O8+P8+S8)/Q8</f>
-        <v>16.222222222222221</v>
-      </c>
-      <c r="Y8" s="1">
         <f t="shared" si="4"/>
         <v>16.222222222222221</v>
       </c>
+      <c r="Y8" s="1">
+        <f t="shared" si="5"/>
+        <v>16.222222222222221</v>
+      </c>
       <c r="Z8" s="1">
         <v>45.8</v>
       </c>
@@ -1702,11 +1702,11 @@
         <v>37</v>
       </c>
       <c r="AF8" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG8" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH8" s="1"/>
@@ -1779,7 +1779,7 @@
         <v>210.96819999999997</v>
       </c>
       <c r="R9" s="5">
-        <f t="shared" ref="R9:R50" si="9">14*Q9-P9-O9-F9</f>
+        <f t="shared" ref="R9:R50" si="10">14*Q9-P9-O9-F9</f>
         <v>794.39879999999948</v>
       </c>
       <c r="S9" s="5">
@@ -1787,7 +1787,7 @@
         <v>850</v>
       </c>
       <c r="T9" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>350</v>
       </c>
       <c r="U9" s="5">
@@ -1799,11 +1799,11 @@
       </c>
       <c r="W9" s="1"/>
       <c r="X9" s="1">
-        <f>(F9+O9+P9+S9)/Q9</f>
+        <f t="shared" si="4"/>
         <v>14.263552516445609</v>
       </c>
       <c r="Y9" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.23450927675356</v>
       </c>
       <c r="Z9" s="1">
@@ -1823,11 +1823,11 @@
       </c>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>350</v>
       </c>
       <c r="AG9" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="AH9" s="1"/>
@@ -1901,24 +1901,24 @@
       </c>
       <c r="R10" s="5"/>
       <c r="S10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T10" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1">
-        <f>(F10+O10+P10+S10)/Q10</f>
-        <v>80.90721137942441</v>
-      </c>
-      <c r="Y10" s="1">
         <f t="shared" si="4"/>
         <v>80.90721137942441</v>
       </c>
+      <c r="Y10" s="1">
+        <f t="shared" si="5"/>
+        <v>80.90721137942441</v>
+      </c>
       <c r="Z10" s="1">
         <v>6.8614000000000006</v>
       </c>
@@ -1938,11 +1938,11 @@
         <v>111</v>
       </c>
       <c r="AF10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG10" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH10" s="1"/>
@@ -2015,29 +2015,29 @@
         <v>35.412799999999997</v>
       </c>
       <c r="R11" s="5">
+        <f t="shared" si="10"/>
+        <v>208.24319999999994</v>
+      </c>
+      <c r="S11" s="5">
         <f t="shared" si="9"/>
-        <v>208.24319999999994</v>
-      </c>
-      <c r="S11" s="5">
-        <f t="shared" si="8"/>
         <v>208</v>
       </c>
       <c r="T11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>86</v>
       </c>
       <c r="U11" s="5">
-        <f t="shared" ref="U11:U12" si="10">ROUND(S11/1.7,0)</f>
+        <f t="shared" ref="U11:U12" si="11">ROUND(S11/1.7,0)</f>
         <v>122</v>
       </c>
       <c r="V11" s="5"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1">
-        <f>(F11+O11+P11+S11)/Q11</f>
+        <f t="shared" si="4"/>
         <v>13.993132426693174</v>
       </c>
       <c r="Y11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.1195499932227904</v>
       </c>
       <c r="Z11" s="1">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="AG11" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>122</v>
       </c>
       <c r="AH11" s="1"/>
@@ -2134,29 +2134,29 @@
         <v>97.275999999999996</v>
       </c>
       <c r="R12" s="5">
+        <f t="shared" si="10"/>
+        <v>433.67400000000004</v>
+      </c>
+      <c r="S12" s="5">
         <f t="shared" si="9"/>
-        <v>433.67400000000004</v>
-      </c>
-      <c r="S12" s="5">
-        <f t="shared" si="8"/>
         <v>434</v>
       </c>
       <c r="T12" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>179</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>255</v>
       </c>
       <c r="V12" s="5"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1">
-        <f>(F12+O12+P12+S12)/Q12</f>
+        <f t="shared" si="4"/>
         <v>14.003351289115507</v>
       </c>
       <c r="Y12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.541819153748099</v>
       </c>
       <c r="Z12" s="1">
@@ -2176,11 +2176,11 @@
       </c>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>179</v>
       </c>
       <c r="AG12" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>255</v>
       </c>
       <c r="AH12" s="1"/>
@@ -2251,7 +2251,7 @@
         <v>17.399999999999999</v>
       </c>
       <c r="R13" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>51.599999999999966</v>
       </c>
       <c r="S13" s="5">
@@ -2259,7 +2259,7 @@
         <v>70</v>
       </c>
       <c r="T13" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="U13" s="5"/>
@@ -2268,11 +2268,11 @@
       </c>
       <c r="W13" s="1"/>
       <c r="X13" s="1">
-        <f>(F13+O13+P13+S13)/Q13</f>
+        <f t="shared" si="4"/>
         <v>15.057471264367818</v>
       </c>
       <c r="Y13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.03448275862069</v>
       </c>
       <c r="Z13" s="1">
@@ -2294,11 +2294,11 @@
         <v>43</v>
       </c>
       <c r="AF13" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>17.5</v>
       </c>
       <c r="AG13" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH13" s="1"/>
@@ -2371,15 +2371,15 @@
         <v>15.771799999999999</v>
       </c>
       <c r="R14" s="5">
+        <f t="shared" si="10"/>
+        <v>128.95519999999999</v>
+      </c>
+      <c r="S14" s="5">
         <f t="shared" si="9"/>
-        <v>128.95519999999999</v>
-      </c>
-      <c r="S14" s="5">
-        <f t="shared" si="8"/>
         <v>129</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="U14" s="5">
@@ -2389,11 +2389,11 @@
       <c r="V14" s="5"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1">
-        <f>(F14+O14+P14+S14)/Q14</f>
+        <f t="shared" si="4"/>
         <v>14.002840512814011</v>
       </c>
       <c r="Y14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.823685311758962</v>
       </c>
       <c r="Z14" s="1">
@@ -2413,11 +2413,11 @@
       </c>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>53</v>
       </c>
       <c r="AG14" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="AH14" s="1"/>
@@ -2489,24 +2489,24 @@
       </c>
       <c r="R15" s="5"/>
       <c r="S15" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T15" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1">
-        <f>(F15+O15+P15+S15)/Q15</f>
-        <v>30.857142857142858</v>
-      </c>
-      <c r="Y15" s="1">
         <f t="shared" si="4"/>
         <v>30.857142857142858</v>
       </c>
+      <c r="Y15" s="1">
+        <f t="shared" si="5"/>
+        <v>30.857142857142858</v>
+      </c>
       <c r="Z15" s="1">
         <v>13.6</v>
       </c>
@@ -2526,11 +2526,11 @@
         <v>111</v>
       </c>
       <c r="AF15" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG15" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH15" s="1"/>
@@ -2603,15 +2603,15 @@
         <v>83.6</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>578.39999999999986</v>
       </c>
       <c r="S16" s="5">
-        <f t="shared" ref="S16:S18" si="11">V16</f>
+        <f t="shared" ref="S16:S18" si="12">V16</f>
         <v>1850</v>
       </c>
       <c r="T16" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1850</v>
       </c>
       <c r="U16" s="5"/>
@@ -2622,11 +2622,11 @@
         <v>140</v>
       </c>
       <c r="X16" s="1">
-        <f>(F16+O16+P16+S16)/Q16</f>
+        <f t="shared" si="4"/>
         <v>29.210526315789476</v>
       </c>
       <c r="Y16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.0813397129186608</v>
       </c>
       <c r="Z16" s="1">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>740</v>
       </c>
       <c r="AG16" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH16" s="1"/>
@@ -2723,15 +2723,15 @@
         <v>60.511800000000008</v>
       </c>
       <c r="R17" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>285.40320000000014</v>
       </c>
       <c r="S17" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>124</v>
       </c>
       <c r="U17" s="5">
@@ -2743,11 +2743,11 @@
       </c>
       <c r="W17" s="1"/>
       <c r="X17" s="1">
-        <f>(F17+O17+P17+S17)/Q17</f>
+        <f t="shared" si="4"/>
         <v>14.241222373156969</v>
       </c>
       <c r="Y17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.2835116456624966</v>
       </c>
       <c r="Z17" s="1">
@@ -2767,11 +2767,11 @@
       </c>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>124</v>
       </c>
       <c r="AG17" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>176</v>
       </c>
       <c r="AH17" s="1"/>
@@ -2842,15 +2842,15 @@
         <v>2.4303999999999997</v>
       </c>
       <c r="R18" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21.933599999999998</v>
       </c>
       <c r="S18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="U18" s="5"/>
@@ -2859,11 +2859,11 @@
       </c>
       <c r="W18" s="1"/>
       <c r="X18" s="1">
-        <f>(F18+O18+P18+S18)/Q18</f>
+        <f t="shared" si="4"/>
         <v>17.31895984200132</v>
       </c>
       <c r="Y18" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.9753127057274531</v>
       </c>
       <c r="Z18" s="1">
@@ -2883,11 +2883,11 @@
       </c>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="AG18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH18" s="1"/>
@@ -2960,15 +2960,15 @@
         <v>54.6</v>
       </c>
       <c r="R19" s="5">
+        <f t="shared" si="10"/>
+        <v>367.4</v>
+      </c>
+      <c r="S19" s="5">
         <f t="shared" si="9"/>
-        <v>367.4</v>
-      </c>
-      <c r="S19" s="5">
-        <f t="shared" si="8"/>
         <v>367</v>
       </c>
       <c r="T19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>151</v>
       </c>
       <c r="U19" s="5">
@@ -2978,11 +2978,11 @@
       <c r="V19" s="5"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1">
-        <f>(F19+O19+P19+S19)/Q19</f>
+        <f t="shared" si="4"/>
         <v>13.992673992673993</v>
       </c>
       <c r="Y19" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.271062271062271</v>
       </c>
       <c r="Z19" s="1">
@@ -3004,11 +3004,11 @@
         <v>43</v>
       </c>
       <c r="AF19" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>60.400000000000006</v>
       </c>
       <c r="AG19" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>86.4</v>
       </c>
       <c r="AH19" s="1"/>
@@ -3082,11 +3082,11 @@
       </c>
       <c r="R20" s="5"/>
       <c r="S20" s="5">
-        <f t="shared" ref="S20:S21" si="12">V20</f>
+        <f t="shared" ref="S20:S21" si="13">V20</f>
         <v>60</v>
       </c>
       <c r="T20" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="U20" s="5"/>
@@ -3095,11 +3095,11 @@
       </c>
       <c r="W20" s="1"/>
       <c r="X20" s="1">
-        <f>(F20+O20+P20+S20)/Q20</f>
+        <f t="shared" si="4"/>
         <v>17.264654372190645</v>
       </c>
       <c r="Y20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15.892843261435187</v>
       </c>
       <c r="Z20" s="1">
@@ -3119,11 +3119,11 @@
       </c>
       <c r="AE20" s="1"/>
       <c r="AF20" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>60</v>
       </c>
       <c r="AG20" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH20" s="1"/>
@@ -3196,15 +3196,15 @@
         <v>34.799999999999997</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>68.199999999999932</v>
       </c>
       <c r="S21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="T21" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="U21" s="5"/>
@@ -3213,11 +3213,11 @@
       </c>
       <c r="W21" s="1"/>
       <c r="X21" s="1">
-        <f>(F21+O21+P21+S21)/Q21</f>
+        <f t="shared" si="4"/>
         <v>14.913793103448278</v>
       </c>
       <c r="Y21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.040229885057473</v>
       </c>
       <c r="Z21" s="1">
@@ -3237,11 +3237,11 @@
       </c>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="AG21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH21" s="1"/>
@@ -3305,24 +3305,24 @@
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T22" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1">
-        <f>(F22+O22+P22+S22)/Q22</f>
-        <v>16.28125</v>
-      </c>
-      <c r="Y22" s="1">
         <f t="shared" si="4"/>
         <v>16.28125</v>
       </c>
+      <c r="Y22" s="1">
+        <f t="shared" si="5"/>
+        <v>16.28125</v>
+      </c>
       <c r="Z22" s="1">
         <v>0</v>
       </c>
@@ -3340,11 +3340,11 @@
       </c>
       <c r="AE22" s="1"/>
       <c r="AF22" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH22" s="1"/>
@@ -3415,15 +3415,15 @@
         <v>3.8</v>
       </c>
       <c r="R23" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>19.199999999999996</v>
       </c>
       <c r="S23" s="5">
-        <f t="shared" ref="S23:S24" si="13">V23</f>
+        <f t="shared" ref="S23:S24" si="14">V23</f>
         <v>40</v>
       </c>
       <c r="T23" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="U23" s="5"/>
@@ -3432,11 +3432,11 @@
       </c>
       <c r="W23" s="1"/>
       <c r="X23" s="1">
-        <f>(F23+O23+P23+S23)/Q23</f>
+        <f t="shared" si="4"/>
         <v>19.473684210526315</v>
       </c>
       <c r="Y23" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.9473684210526319</v>
       </c>
       <c r="Z23" s="1">
@@ -3458,11 +3458,11 @@
         <v>54</v>
       </c>
       <c r="AF23" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="AG23" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH23" s="1"/>
@@ -3535,19 +3535,19 @@
         <v>53.355600000000003</v>
       </c>
       <c r="R24" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>89.455400000000083</v>
       </c>
       <c r="S24" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
       <c r="T24" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>49</v>
       </c>
       <c r="U24" s="5">
-        <f t="shared" ref="U24:U25" si="14">ROUND(S24/1.7,0)</f>
+        <f t="shared" ref="U24:U25" si="15">ROUND(S24/1.7,0)</f>
         <v>71</v>
       </c>
       <c r="V24" s="5">
@@ -3555,11 +3555,11 @@
       </c>
       <c r="W24" s="1"/>
       <c r="X24" s="1">
-        <f>(F24+O24+P24+S24)/Q24</f>
+        <f t="shared" si="4"/>
         <v>14.572472242838614</v>
       </c>
       <c r="Y24" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.323411225813222</v>
       </c>
       <c r="Z24" s="1">
@@ -3581,11 +3581,11 @@
         <v>56</v>
       </c>
       <c r="AF24" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="AG24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>71</v>
       </c>
       <c r="AH24" s="1"/>
@@ -3658,29 +3658,29 @@
         <v>83</v>
       </c>
       <c r="R25" s="5">
+        <f t="shared" si="10"/>
+        <v>336</v>
+      </c>
+      <c r="S25" s="5">
         <f t="shared" si="9"/>
         <v>336</v>
       </c>
-      <c r="S25" s="5">
-        <f t="shared" si="8"/>
-        <v>336</v>
-      </c>
       <c r="T25" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>138</v>
       </c>
       <c r="U25" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>198</v>
       </c>
       <c r="V25" s="5"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1">
-        <f>(F25+O25+P25+S25)/Q25</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="Y25" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.9518072289156621</v>
       </c>
       <c r="Z25" s="1">
@@ -3700,11 +3700,11 @@
       </c>
       <c r="AE25" s="1"/>
       <c r="AF25" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.42</v>
       </c>
       <c r="AG25" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17.82</v>
       </c>
       <c r="AH25" s="1"/>
@@ -3778,24 +3778,24 @@
       </c>
       <c r="R26" s="5"/>
       <c r="S26" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T26" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U26" s="5"/>
       <c r="V26" s="5"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1">
-        <f>(F26+O26+P26+S26)/Q26</f>
-        <v>48.3</v>
-      </c>
-      <c r="Y26" s="1">
         <f t="shared" si="4"/>
         <v>48.3</v>
       </c>
+      <c r="Y26" s="1">
+        <f t="shared" si="5"/>
+        <v>48.3</v>
+      </c>
       <c r="Z26" s="1">
         <v>40.799999999999997</v>
       </c>
@@ -3815,11 +3815,11 @@
         <v>43</v>
       </c>
       <c r="AF26" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG26" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH26" s="1"/>
@@ -3891,24 +3891,24 @@
       </c>
       <c r="R27" s="5"/>
       <c r="S27" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T27" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U27" s="5"/>
       <c r="V27" s="5"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1">
-        <f>(F27+O27+P27+S27)/Q27</f>
-        <v>26.911764705882355</v>
-      </c>
-      <c r="Y27" s="1">
         <f t="shared" si="4"/>
         <v>26.911764705882355</v>
       </c>
+      <c r="Y27" s="1">
+        <f t="shared" si="5"/>
+        <v>26.911764705882355</v>
+      </c>
       <c r="Z27" s="1">
         <v>29.4</v>
       </c>
@@ -3928,11 +3928,11 @@
         <v>91</v>
       </c>
       <c r="AF27" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG27" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH27" s="1"/>
@@ -4010,7 +4010,7 @@
         <v>100</v>
       </c>
       <c r="T28" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="U28" s="5"/>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="W28" s="1"/>
       <c r="X28" s="1">
-        <f>(F28+O28+P28+S28)/Q28</f>
+        <f t="shared" si="4"/>
         <v>16.570048880665876</v>
       </c>
       <c r="Y28" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14.204092158746235</v>
       </c>
       <c r="Z28" s="1">
@@ -4043,11 +4043,11 @@
       </c>
       <c r="AE28" s="1"/>
       <c r="AF28" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="AG28" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH28" s="1"/>
@@ -4117,22 +4117,22 @@
         <v>80</v>
       </c>
       <c r="S29" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="U29" s="5"/>
       <c r="V29" s="5"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1">
-        <f>(F29+O29+P29+S29)/Q29</f>
+        <f t="shared" si="4"/>
         <v>-200</v>
       </c>
       <c r="Y29" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z29" s="1">
@@ -4154,11 +4154,11 @@
         <v>62</v>
       </c>
       <c r="AF29" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="AG29" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH29" s="1"/>
@@ -4231,7 +4231,7 @@
         <v>7</v>
       </c>
       <c r="R30" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="S30" s="5">
@@ -4239,7 +4239,7 @@
         <v>50</v>
       </c>
       <c r="T30" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="U30" s="5"/>
@@ -4248,11 +4248,11 @@
       </c>
       <c r="W30" s="1"/>
       <c r="X30" s="1">
-        <f>(F30+O30+P30+S30)/Q30</f>
+        <f t="shared" si="4"/>
         <v>19.285714285714285</v>
       </c>
       <c r="Y30" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.142857142857142</v>
       </c>
       <c r="Z30" s="1">
@@ -4272,11 +4272,11 @@
       </c>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="AG30" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH30" s="1"/>
@@ -4349,29 +4349,29 @@
         <v>134.6</v>
       </c>
       <c r="R31" s="5">
+        <f t="shared" si="10"/>
+        <v>1222.7449999999999</v>
+      </c>
+      <c r="S31" s="5">
         <f t="shared" si="9"/>
-        <v>1222.7449999999999</v>
-      </c>
-      <c r="S31" s="5">
-        <f t="shared" si="8"/>
         <v>1223</v>
       </c>
       <c r="T31" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>504</v>
       </c>
       <c r="U31" s="5">
-        <f t="shared" ref="U31:U35" si="15">ROUND(S31/1.7,0)</f>
+        <f t="shared" ref="U31:U35" si="16">ROUND(S31/1.7,0)</f>
         <v>719</v>
       </c>
       <c r="V31" s="5"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1">
-        <f>(F31+O31+P31+S31)/Q31</f>
+        <f t="shared" si="4"/>
         <v>14.001894502228826</v>
       </c>
       <c r="Y31" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.9157132243684991</v>
       </c>
       <c r="Z31" s="1">
@@ -4393,11 +4393,11 @@
         <v>43</v>
       </c>
       <c r="AF31" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>201.60000000000002</v>
       </c>
       <c r="AG31" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>287.60000000000002</v>
       </c>
       <c r="AH31" s="1"/>
@@ -4474,25 +4474,25 @@
         <v>592</v>
       </c>
       <c r="S32" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>592</v>
       </c>
       <c r="T32" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>244</v>
       </c>
       <c r="U32" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>348</v>
       </c>
       <c r="V32" s="5"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1">
-        <f>(F32+O32+P32+S32)/Q32</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="Y32" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.31358885017421606</v>
       </c>
       <c r="Z32" s="1">
@@ -4514,11 +4514,11 @@
         <v>43</v>
       </c>
       <c r="AF32" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>97.600000000000009</v>
       </c>
       <c r="AG32" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>139.20000000000002</v>
       </c>
       <c r="AH32" s="1"/>
@@ -4591,29 +4591,29 @@
         <v>133.94</v>
       </c>
       <c r="R33" s="5">
+        <f t="shared" si="10"/>
+        <v>749.8599999999999</v>
+      </c>
+      <c r="S33" s="5">
         <f t="shared" si="9"/>
-        <v>749.8599999999999</v>
-      </c>
-      <c r="S33" s="5">
-        <f t="shared" si="8"/>
         <v>750</v>
       </c>
       <c r="T33" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>309</v>
       </c>
       <c r="U33" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>441</v>
       </c>
       <c r="V33" s="5"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1">
-        <f>(F33+O33+P33+S33)/Q33</f>
+        <f t="shared" si="4"/>
         <v>14.001045244139167</v>
       </c>
       <c r="Y33" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.4015230700313577</v>
       </c>
       <c r="Z33" s="1">
@@ -4635,11 +4635,11 @@
         <v>43</v>
       </c>
       <c r="AF33" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>123.60000000000001</v>
       </c>
       <c r="AG33" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>176.4</v>
       </c>
       <c r="AH33" s="1"/>
@@ -4712,29 +4712,29 @@
         <v>60</v>
       </c>
       <c r="R34" s="5">
+        <f t="shared" si="10"/>
+        <v>152</v>
+      </c>
+      <c r="S34" s="5">
         <f t="shared" si="9"/>
         <v>152</v>
       </c>
-      <c r="S34" s="5">
-        <f t="shared" si="8"/>
-        <v>152</v>
-      </c>
       <c r="T34" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>63</v>
       </c>
       <c r="U34" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>89</v>
       </c>
       <c r="V34" s="5"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1">
-        <f>(F34+O34+P34+S34)/Q34</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="Y34" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.466666666666667</v>
       </c>
       <c r="Z34" s="1">
@@ -4756,11 +4756,11 @@
         <v>43</v>
       </c>
       <c r="AF34" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.3000000000000007</v>
       </c>
       <c r="AG34" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.9</v>
       </c>
       <c r="AH34" s="1"/>
@@ -4833,29 +4833,29 @@
         <v>41.2</v>
       </c>
       <c r="R35" s="5">
+        <f t="shared" si="10"/>
+        <v>351.80000000000007</v>
+      </c>
+      <c r="S35" s="5">
         <f t="shared" si="9"/>
-        <v>351.80000000000007</v>
-      </c>
-      <c r="S35" s="5">
-        <f t="shared" si="8"/>
         <v>352</v>
       </c>
       <c r="T35" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>145</v>
       </c>
       <c r="U35" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>207</v>
       </c>
       <c r="V35" s="5"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1">
-        <f>(F35+O35+P35+S35)/Q35</f>
+        <f t="shared" si="4"/>
         <v>14.004854368932039</v>
       </c>
       <c r="Y35" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.4611650485436893</v>
       </c>
       <c r="Z35" s="1">
@@ -4877,11 +4877,11 @@
         <v>43</v>
       </c>
       <c r="AF35" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.5</v>
       </c>
       <c r="AG35" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20.700000000000003</v>
       </c>
       <c r="AH35" s="1"/>
@@ -4954,26 +4954,26 @@
         <v>21.2</v>
       </c>
       <c r="R36" s="5">
+        <f t="shared" si="10"/>
+        <v>95.800000000000011</v>
+      </c>
+      <c r="S36" s="5">
         <f t="shared" si="9"/>
-        <v>95.800000000000011</v>
-      </c>
-      <c r="S36" s="5">
-        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="T36" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>96</v>
       </c>
       <c r="U36" s="5"/>
       <c r="V36" s="5"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1">
-        <f>(F36+O36+P36+S36)/Q36</f>
+        <f t="shared" si="4"/>
         <v>14.009433962264151</v>
       </c>
       <c r="Y36" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.4811320754716988</v>
       </c>
       <c r="Z36" s="1">
@@ -4993,11 +4993,11 @@
       </c>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.6000000000000014</v>
       </c>
       <c r="AG36" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH36" s="1"/>
@@ -5063,24 +5063,24 @@
       </c>
       <c r="R37" s="5"/>
       <c r="S37" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T37" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U37" s="5"/>
       <c r="V37" s="5"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1">
-        <f>(F37+O37+P37+S37)/Q37</f>
-        <v>22.799092409240924</v>
-      </c>
-      <c r="Y37" s="1">
         <f t="shared" si="4"/>
         <v>22.799092409240924</v>
       </c>
+      <c r="Y37" s="1">
+        <f t="shared" si="5"/>
+        <v>22.799092409240924</v>
+      </c>
       <c r="Z37" s="1">
         <v>0</v>
       </c>
@@ -5100,11 +5100,11 @@
         <v>111</v>
       </c>
       <c r="AF37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG37" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH37" s="1"/>
@@ -5159,7 +5159,7 @@
         <v>72</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="16">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="17">E38-K38</f>
         <v>-19</v>
       </c>
       <c r="M38" s="1"/>
@@ -5171,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="1">
-        <f t="shared" ref="Q38:Q69" si="17">E38/5</f>
+        <f t="shared" ref="Q38:Q69" si="18">E38/5</f>
         <v>10.6</v>
       </c>
       <c r="R38" s="5">
@@ -5179,22 +5179,22 @@
         <v>100</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="T38" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
       <c r="W38" s="1"/>
       <c r="X38" s="1">
-        <f>(F38+O38+P38+S38)/Q38</f>
+        <f t="shared" ref="X38:X70" si="19">(F38+O38+P38+S38)/Q38</f>
         <v>10</v>
       </c>
       <c r="Y38" s="1">
-        <f t="shared" ref="Y38:Y69" si="18">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="Y38:Y69" si="20">(F38+O38+P38)/Q38</f>
         <v>0.56603773584905659</v>
       </c>
       <c r="Z38" s="1">
@@ -5216,11 +5216,11 @@
         <v>43</v>
       </c>
       <c r="AF38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
       <c r="AG38" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH38" s="1"/>
@@ -5277,7 +5277,7 @@
         <v>282</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-136</v>
       </c>
       <c r="M39" s="1"/>
@@ -5289,27 +5289,27 @@
         <v>210</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>29.2</v>
       </c>
       <c r="R39" s="5"/>
       <c r="S39" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U39" s="5"/>
       <c r="V39" s="5"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1">
-        <f>(F39+O39+P39+S39)/Q39</f>
+        <f t="shared" si="19"/>
         <v>15.958904109589042</v>
       </c>
       <c r="Y39" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>15.958904109589042</v>
       </c>
       <c r="Z39" s="1">
@@ -5329,11 +5329,11 @@
       </c>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG39" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH39" s="1"/>
@@ -5390,7 +5390,7 @@
         <v>109.8</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-0.91400000000000148</v>
       </c>
       <c r="M40" s="1"/>
@@ -5402,19 +5402,19 @@
         <v>50</v>
       </c>
       <c r="Q40" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>21.777200000000001</v>
       </c>
       <c r="R40" s="5">
+        <f t="shared" si="10"/>
+        <v>156.29480000000001</v>
+      </c>
+      <c r="S40" s="5">
         <f t="shared" si="9"/>
-        <v>156.29480000000001</v>
-      </c>
-      <c r="S40" s="5">
-        <f t="shared" si="8"/>
         <v>156</v>
       </c>
       <c r="T40" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>64</v>
       </c>
       <c r="U40" s="5">
@@ -5424,11 +5424,11 @@
       <c r="V40" s="5"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1">
-        <f>(F40+O40+P40+S40)/Q40</f>
+        <f t="shared" si="19"/>
         <v>13.986462906158735</v>
       </c>
       <c r="Y40" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.8230075491798763</v>
       </c>
       <c r="Z40" s="1">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>64</v>
       </c>
       <c r="AG40" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="AH40" s="1"/>
@@ -5509,7 +5509,7 @@
         <v>63.850999999999999</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-7.6270000000000024</v>
       </c>
       <c r="M41" s="1"/>
@@ -5521,11 +5521,11 @@
         <v>40</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>11.2448</v>
       </c>
       <c r="R41" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>22.505200000000002</v>
       </c>
       <c r="S41" s="5">
@@ -5533,7 +5533,7 @@
         <v>50</v>
       </c>
       <c r="T41" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="U41" s="5"/>
@@ -5542,11 +5542,11 @@
       </c>
       <c r="W41" s="1"/>
       <c r="X41" s="1">
-        <f>(F41+O41+P41+S41)/Q41</f>
+        <f t="shared" si="19"/>
         <v>16.445112407512806</v>
       </c>
       <c r="Y41" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>11.998612692088788</v>
       </c>
       <c r="Z41" s="1">
@@ -5566,11 +5566,11 @@
       </c>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="AG41" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH41" s="1"/>
@@ -5627,7 +5627,7 @@
         <v>116.22</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-5.3499999999999943</v>
       </c>
       <c r="M42" s="1"/>
@@ -5639,33 +5639,33 @@
         <v>50</v>
       </c>
       <c r="Q42" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>22.173999999999999</v>
       </c>
       <c r="R42" s="5">
+        <f t="shared" si="10"/>
+        <v>128.69799999999998</v>
+      </c>
+      <c r="S42" s="5">
         <f t="shared" si="9"/>
-        <v>128.69799999999998</v>
-      </c>
-      <c r="S42" s="5">
-        <f t="shared" si="8"/>
         <v>129</v>
       </c>
       <c r="T42" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="U42" s="5">
-        <f t="shared" ref="U42:U43" si="19">ROUND(S42/1.7,0)</f>
+        <f t="shared" ref="U42:U43" si="21">ROUND(S42/1.7,0)</f>
         <v>76</v>
       </c>
       <c r="V42" s="5"/>
       <c r="W42" s="1"/>
       <c r="X42" s="1">
-        <f>(F42+O42+P42+S42)/Q42</f>
+        <f t="shared" si="19"/>
         <v>14.01361955443312</v>
       </c>
       <c r="Y42" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>8.1959953098223153</v>
       </c>
       <c r="Z42" s="1">
@@ -5685,11 +5685,11 @@
       </c>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>53</v>
       </c>
       <c r="AG42" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="AH42" s="1"/>
@@ -5746,7 +5746,7 @@
         <v>198.1</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-5.5529999999999973</v>
       </c>
       <c r="M43" s="1"/>
@@ -5758,33 +5758,33 @@
         <v>110</v>
       </c>
       <c r="Q43" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>38.509399999999999</v>
       </c>
       <c r="R43" s="5">
+        <f t="shared" si="10"/>
+        <v>222.97959999999995</v>
+      </c>
+      <c r="S43" s="5">
         <f t="shared" si="9"/>
-        <v>222.97959999999995</v>
-      </c>
-      <c r="S43" s="5">
-        <f t="shared" si="8"/>
         <v>223</v>
       </c>
       <c r="T43" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>92</v>
       </c>
       <c r="U43" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>131</v>
       </c>
       <c r="V43" s="5"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1">
-        <f>(F43+O43+P43+S43)/Q43</f>
+        <f t="shared" si="19"/>
         <v>14.000529740790562</v>
       </c>
       <c r="Y43" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>8.2097358047645503</v>
       </c>
       <c r="Z43" s="1">
@@ -5804,11 +5804,11 @@
       </c>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
       <c r="AG43" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>131</v>
       </c>
       <c r="AH43" s="1"/>
@@ -5865,7 +5865,7 @@
         <v>2401</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-38</v>
       </c>
       <c r="M44" s="1"/>
@@ -5877,29 +5877,29 @@
         <v>850</v>
       </c>
       <c r="Q44" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>472.6</v>
       </c>
       <c r="R44" s="18">
         <v>0</v>
       </c>
       <c r="S44" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T44" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U44" s="5"/>
       <c r="V44" s="5"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1">
-        <f>(F44+O44+P44+S44)/Q44</f>
+        <f t="shared" si="19"/>
         <v>5.0190435886584845</v>
       </c>
       <c r="Y44" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5.0190435886584845</v>
       </c>
       <c r="Z44" s="1">
@@ -5919,11 +5919,11 @@
       </c>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG44" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH44" s="1"/>
@@ -5980,7 +5980,7 @@
         <v>10.6</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.22300000000000075</v>
       </c>
       <c r="M45" s="1"/>
@@ -5992,30 +5992,30 @@
         <v>0</v>
       </c>
       <c r="Q45" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.1646000000000001</v>
       </c>
       <c r="R45" s="5">
+        <f t="shared" si="10"/>
+        <v>19.4634</v>
+      </c>
+      <c r="S45" s="5">
         <f t="shared" si="9"/>
-        <v>19.4634</v>
-      </c>
-      <c r="S45" s="5">
-        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="T45" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="U45" s="5"/>
       <c r="V45" s="5"/>
       <c r="W45" s="1"/>
       <c r="X45" s="1">
-        <f>(F45+O45+P45+S45)/Q45</f>
+        <f t="shared" si="19"/>
         <v>13.785918876466784</v>
       </c>
       <c r="Y45" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5.0083156241337887</v>
       </c>
       <c r="Z45" s="1">
@@ -6035,11 +6035,11 @@
       </c>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="AG45" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH45" s="1"/>
@@ -6096,7 +6096,7 @@
         <v>1225</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-146</v>
       </c>
       <c r="M46" s="1"/>
@@ -6108,33 +6108,33 @@
         <v>900</v>
       </c>
       <c r="Q46" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>215.8</v>
       </c>
       <c r="R46" s="5">
+        <f t="shared" si="10"/>
+        <v>712.20000000000027</v>
+      </c>
+      <c r="S46" s="5">
         <f t="shared" si="9"/>
-        <v>712.20000000000027</v>
-      </c>
-      <c r="S46" s="5">
-        <f t="shared" si="8"/>
         <v>712</v>
       </c>
       <c r="T46" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>293</v>
       </c>
       <c r="U46" s="5">
-        <f t="shared" ref="U46:U47" si="20">ROUND(S46/1.7,0)</f>
+        <f t="shared" ref="U46:U47" si="22">ROUND(S46/1.7,0)</f>
         <v>419</v>
       </c>
       <c r="V46" s="5"/>
       <c r="W46" s="1"/>
       <c r="X46" s="1">
-        <f>(F46+O46+P46+S46)/Q46</f>
+        <f t="shared" si="19"/>
         <v>13.999073215940685</v>
       </c>
       <c r="Y46" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>10.699721964782205</v>
       </c>
       <c r="Z46" s="1">
@@ -6156,11 +6156,11 @@
         <v>33</v>
       </c>
       <c r="AF46" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>102.55</v>
       </c>
       <c r="AG46" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>146.64999999999998</v>
       </c>
       <c r="AH46" s="1"/>
@@ -6217,7 +6217,7 @@
         <v>470</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-43</v>
       </c>
       <c r="M47" s="1"/>
@@ -6229,33 +6229,33 @@
         <v>80</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>85.4</v>
       </c>
       <c r="R47" s="5">
+        <f t="shared" si="10"/>
+        <v>721.60000000000014</v>
+      </c>
+      <c r="S47" s="5">
         <f t="shared" si="9"/>
-        <v>721.60000000000014</v>
-      </c>
-      <c r="S47" s="5">
-        <f t="shared" si="8"/>
         <v>722</v>
       </c>
       <c r="T47" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>297</v>
       </c>
       <c r="U47" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>425</v>
       </c>
       <c r="V47" s="5"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1">
-        <f>(F47+O47+P47+S47)/Q47</f>
+        <f t="shared" si="19"/>
         <v>14.004683840749413</v>
       </c>
       <c r="Y47" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5.5503512880562056</v>
       </c>
       <c r="Z47" s="1">
@@ -6277,11 +6277,11 @@
         <v>43</v>
       </c>
       <c r="AF47" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>121.77</v>
       </c>
       <c r="AG47" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>174.25</v>
       </c>
       <c r="AH47" s="1"/>
@@ -6338,7 +6338,7 @@
         <v>67</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="M48" s="1"/>
@@ -6350,27 +6350,27 @@
         <v>80</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>12.6</v>
       </c>
       <c r="R48" s="5"/>
       <c r="S48" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T48" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U48" s="5"/>
       <c r="V48" s="5"/>
       <c r="W48" s="1"/>
       <c r="X48" s="1">
-        <f>(F48+O48+P48+S48)/Q48</f>
+        <f t="shared" si="19"/>
         <v>18.888888888888889</v>
       </c>
       <c r="Y48" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>18.888888888888889</v>
       </c>
       <c r="Z48" s="1">
@@ -6390,11 +6390,11 @@
       </c>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH48" s="1"/>
@@ -6451,7 +6451,7 @@
         <v>225</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-12</v>
       </c>
       <c r="M49" s="1"/>
@@ -6463,33 +6463,33 @@
         <v>160</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>42.6</v>
       </c>
       <c r="R49" s="5">
+        <f t="shared" si="10"/>
+        <v>137.39999999999998</v>
+      </c>
+      <c r="S49" s="5">
         <f t="shared" si="9"/>
-        <v>137.39999999999998</v>
-      </c>
-      <c r="S49" s="5">
-        <f t="shared" si="8"/>
         <v>137</v>
       </c>
       <c r="T49" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>56</v>
       </c>
       <c r="U49" s="5">
-        <f t="shared" ref="U49:U50" si="21">ROUND(S49/1.7,0)</f>
+        <f t="shared" ref="U49:U50" si="23">ROUND(S49/1.7,0)</f>
         <v>81</v>
       </c>
       <c r="V49" s="5"/>
       <c r="W49" s="1"/>
       <c r="X49" s="1">
-        <f>(F49+O49+P49+S49)/Q49</f>
+        <f t="shared" si="19"/>
         <v>13.990610328638498</v>
       </c>
       <c r="Y49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>10.774647887323944</v>
       </c>
       <c r="Z49" s="1">
@@ -6511,11 +6511,11 @@
         <v>43</v>
       </c>
       <c r="AF49" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20.16</v>
       </c>
       <c r="AG49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>29.16</v>
       </c>
       <c r="AH49" s="1"/>
@@ -6572,7 +6572,7 @@
         <v>327</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-45</v>
       </c>
       <c r="M50" s="1"/>
@@ -6584,33 +6584,33 @@
         <v>70</v>
       </c>
       <c r="Q50" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>56.4</v>
       </c>
       <c r="R50" s="5">
+        <f t="shared" si="10"/>
+        <v>470.6</v>
+      </c>
+      <c r="S50" s="5">
         <f t="shared" si="9"/>
-        <v>470.6</v>
-      </c>
-      <c r="S50" s="5">
-        <f t="shared" si="8"/>
         <v>471</v>
       </c>
       <c r="T50" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>194</v>
       </c>
       <c r="U50" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>277</v>
       </c>
       <c r="V50" s="5"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1">
-        <f>(F50+O50+P50+S50)/Q50</f>
+        <f t="shared" si="19"/>
         <v>14.00709219858156</v>
       </c>
       <c r="Y50" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5.6560283687943267</v>
       </c>
       <c r="Z50" s="1">
@@ -6632,11 +6632,11 @@
         <v>43</v>
       </c>
       <c r="AF50" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>64.02</v>
       </c>
       <c r="AG50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>91.410000000000011</v>
       </c>
       <c r="AH50" s="1"/>
@@ -6691,7 +6691,7 @@
         <v>220</v>
       </c>
       <c r="L51" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-164</v>
       </c>
       <c r="M51" s="11"/>
@@ -6703,27 +6703,27 @@
         <v>0</v>
       </c>
       <c r="Q51" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>11.2</v>
       </c>
       <c r="R51" s="14"/>
       <c r="S51" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T51" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U51" s="5"/>
       <c r="V51" s="14"/>
       <c r="W51" s="11"/>
       <c r="X51" s="1">
-        <f>(F51+O51+P51+S51)/Q51</f>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="Y51" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="Z51" s="11">
@@ -6745,11 +6745,11 @@
         <v>33</v>
       </c>
       <c r="AF51" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH51" s="1"/>
@@ -6806,7 +6806,7 @@
         <v>215</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-21</v>
       </c>
       <c r="M52" s="1"/>
@@ -6818,19 +6818,19 @@
         <v>40</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>38.799999999999997</v>
       </c>
       <c r="R52" s="5">
-        <f t="shared" ref="R52:R65" si="22">14*Q52-P52-O52-F52</f>
+        <f t="shared" ref="R52:R65" si="24">14*Q52-P52-O52-F52</f>
         <v>283.19999999999993</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>283</v>
       </c>
       <c r="T52" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>117</v>
       </c>
       <c r="U52" s="5">
@@ -6840,11 +6840,11 @@
       <c r="V52" s="5"/>
       <c r="W52" s="1"/>
       <c r="X52" s="1">
-        <f>(F52+O52+P52+S52)/Q52</f>
+        <f t="shared" si="19"/>
         <v>13.994845360824744</v>
       </c>
       <c r="Y52" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.7010309278350517</v>
       </c>
       <c r="Z52" s="1">
@@ -6864,11 +6864,11 @@
       </c>
       <c r="AE52" s="1"/>
       <c r="AF52" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>46.800000000000004</v>
       </c>
       <c r="AG52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>66.400000000000006</v>
       </c>
       <c r="AH52" s="1"/>
@@ -6925,7 +6925,7 @@
         <v>29</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1</v>
       </c>
       <c r="M53" s="1"/>
@@ -6937,27 +6937,27 @@
         <v>0</v>
       </c>
       <c r="Q53" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.6</v>
       </c>
       <c r="R53" s="5"/>
       <c r="S53" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T53" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
       <c r="W53" s="1"/>
       <c r="X53" s="1">
-        <f>(F53+O53+P53+S53)/Q53</f>
+        <f t="shared" si="19"/>
         <v>58.928571428571431</v>
       </c>
       <c r="Y53" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>58.928571428571431</v>
       </c>
       <c r="Z53" s="1">
@@ -6979,11 +6979,11 @@
         <v>91</v>
       </c>
       <c r="AF53" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH53" s="1"/>
@@ -7040,7 +7040,7 @@
         <v>494.3</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-53.314999999999998</v>
       </c>
       <c r="M54" s="1"/>
@@ -7052,19 +7052,19 @@
         <v>260</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>88.197000000000003</v>
       </c>
       <c r="R54" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>583.31500000000005</v>
       </c>
       <c r="S54" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>583</v>
       </c>
       <c r="T54" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>240</v>
       </c>
       <c r="U54" s="5">
@@ -7074,11 +7074,11 @@
       <c r="V54" s="5"/>
       <c r="W54" s="1"/>
       <c r="X54" s="1">
-        <f>(F54+O54+P54+S54)/Q54</f>
+        <f t="shared" si="19"/>
         <v>13.996428449947276</v>
       </c>
       <c r="Y54" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>7.3862262888760384</v>
       </c>
       <c r="Z54" s="1">
@@ -7098,11 +7098,11 @@
       </c>
       <c r="AE54" s="1"/>
       <c r="AF54" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>240</v>
       </c>
       <c r="AG54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>343</v>
       </c>
       <c r="AH54" s="1"/>
@@ -7155,7 +7155,7 @@
         <v>28.1</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-10.076000000000001</v>
       </c>
       <c r="M55" s="1"/>
@@ -7167,27 +7167,27 @@
         <v>50</v>
       </c>
       <c r="Q55" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.6048</v>
       </c>
       <c r="R55" s="5"/>
       <c r="S55" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T55" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U55" s="5"/>
       <c r="V55" s="5"/>
       <c r="W55" s="1"/>
       <c r="X55" s="1">
-        <f>(F55+O55+P55+S55)/Q55</f>
+        <f t="shared" si="19"/>
         <v>27.746893031513537</v>
       </c>
       <c r="Y55" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>27.746893031513537</v>
       </c>
       <c r="Z55" s="1">
@@ -7207,11 +7207,11 @@
       </c>
       <c r="AE55" s="1"/>
       <c r="AF55" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH55" s="1"/>
@@ -7264,7 +7264,7 @@
         <v>27</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-19</v>
       </c>
       <c r="M56" s="1"/>
@@ -7276,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.6</v>
       </c>
       <c r="R56" s="5">
@@ -7284,22 +7284,22 @@
         <v>14.4</v>
       </c>
       <c r="S56" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="T56" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="U56" s="5"/>
       <c r="V56" s="5"/>
       <c r="W56" s="1"/>
       <c r="X56" s="1">
-        <f>(F56+O56+P56+S56)/Q56</f>
+        <f t="shared" si="19"/>
         <v>8.75</v>
       </c>
       <c r="Y56" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Z56" s="1">
@@ -7319,11 +7319,11 @@
       </c>
       <c r="AE56" s="1"/>
       <c r="AF56" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="AG56" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH56" s="1"/>
@@ -7378,7 +7378,7 @@
         <v>33</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-12</v>
       </c>
       <c r="M57" s="1"/>
@@ -7390,27 +7390,27 @@
         <v>50</v>
       </c>
       <c r="Q57" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4.2</v>
       </c>
       <c r="R57" s="5"/>
       <c r="S57" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T57" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U57" s="5"/>
       <c r="V57" s="5"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1">
-        <f>(F57+O57+P57+S57)/Q57</f>
+        <f t="shared" si="19"/>
         <v>23.333333333333332</v>
       </c>
       <c r="Y57" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>23.333333333333332</v>
       </c>
       <c r="Z57" s="1">
@@ -7430,11 +7430,11 @@
       </c>
       <c r="AE57" s="1"/>
       <c r="AF57" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG57" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH57" s="1"/>
@@ -7491,7 +7491,7 @@
         <v>37.5</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-24.488</v>
       </c>
       <c r="M58" s="1"/>
@@ -7503,7 +7503,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.6024000000000003</v>
       </c>
       <c r="R58" s="5">
@@ -7511,22 +7511,22 @@
         <v>22.730400000000003</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
       <c r="T58" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="U58" s="5"/>
       <c r="V58" s="5"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1">
-        <f>(F58+O58+P58+S58)/Q58</f>
+        <f t="shared" si="19"/>
         <v>11.103596679987703</v>
       </c>
       <c r="Y58" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2.2656009837073467</v>
       </c>
       <c r="Z58" s="1">
@@ -7546,11 +7546,11 @@
       </c>
       <c r="AE58" s="1"/>
       <c r="AF58" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="AG58" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH58" s="1"/>
@@ -7607,7 +7607,7 @@
         <v>15.9</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-5.7800000000000011</v>
       </c>
       <c r="M59" s="1"/>
@@ -7619,27 +7619,27 @@
         <v>25</v>
       </c>
       <c r="Q59" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.024</v>
       </c>
       <c r="R59" s="5"/>
       <c r="S59" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T59" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U59" s="5"/>
       <c r="V59" s="5"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1">
-        <f>(F59+O59+P59+S59)/Q59</f>
+        <f t="shared" si="19"/>
         <v>25.427371541501977</v>
       </c>
       <c r="Y59" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>25.427371541501977</v>
       </c>
       <c r="Z59" s="1">
@@ -7659,11 +7659,11 @@
       </c>
       <c r="AE59" s="1"/>
       <c r="AF59" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG59" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH59" s="1"/>
@@ -7716,7 +7716,7 @@
         <v>11</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-7</v>
       </c>
       <c r="M60" s="1"/>
@@ -7728,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.8</v>
       </c>
       <c r="R60" s="5">
@@ -7739,7 +7739,7 @@
         <v>60</v>
       </c>
       <c r="T60" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="U60" s="5"/>
@@ -7748,11 +7748,11 @@
       </c>
       <c r="W60" s="1"/>
       <c r="X60" s="1">
-        <f>(F60+O60+P60+S60)/Q60</f>
+        <f t="shared" si="19"/>
         <v>62.5</v>
       </c>
       <c r="Y60" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-12.5</v>
       </c>
       <c r="Z60" s="1">
@@ -7772,11 +7772,11 @@
       </c>
       <c r="AE60" s="1"/>
       <c r="AF60" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="AG60" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH60" s="1"/>
@@ -7827,7 +7827,7 @@
         <v>25.7</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-21.411999999999999</v>
       </c>
       <c r="M61" s="1"/>
@@ -7835,27 +7835,27 @@
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
       <c r="Q61" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.85760000000000003</v>
       </c>
       <c r="R61" s="5"/>
       <c r="S61" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T61" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U61" s="5"/>
       <c r="V61" s="5"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1">
-        <f>(F61+O61+P61+S61)/Q61</f>
+        <f t="shared" si="19"/>
         <v>18.959888059701495</v>
       </c>
       <c r="Y61" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>18.959888059701495</v>
       </c>
       <c r="Z61" s="1">
@@ -7875,11 +7875,11 @@
       </c>
       <c r="AE61" s="1"/>
       <c r="AF61" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG61" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH61" s="1"/>
@@ -7936,7 +7936,7 @@
         <v>58</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1</v>
       </c>
       <c r="M62" s="1"/>
@@ -7948,30 +7948,30 @@
         <v>0</v>
       </c>
       <c r="Q62" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>11.4</v>
       </c>
       <c r="R62" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>40.599999999999994</v>
       </c>
       <c r="S62" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="T62" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>41</v>
       </c>
       <c r="U62" s="5"/>
       <c r="V62" s="5"/>
       <c r="W62" s="1"/>
       <c r="X62" s="1">
-        <f>(F62+O62+P62+S62)/Q62</f>
+        <f t="shared" si="19"/>
         <v>14.035087719298245</v>
       </c>
       <c r="Y62" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>10.43859649122807</v>
       </c>
       <c r="Z62" s="1">
@@ -7991,11 +7991,11 @@
       </c>
       <c r="AE62" s="1"/>
       <c r="AF62" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10.25</v>
       </c>
       <c r="AG62" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH62" s="1"/>
@@ -8052,7 +8052,7 @@
         <v>18.22</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-2.6909999999999989</v>
       </c>
       <c r="M63" s="1"/>
@@ -8064,30 +8064,30 @@
         <v>10</v>
       </c>
       <c r="Q63" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.1057999999999999</v>
       </c>
       <c r="R63" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7.9122000000000003</v>
       </c>
       <c r="S63" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="T63" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="U63" s="5"/>
       <c r="V63" s="5"/>
       <c r="W63" s="1"/>
       <c r="X63" s="1">
-        <f>(F63+O63+P63+S63)/Q63</f>
+        <f t="shared" si="19"/>
         <v>14.028269688969027</v>
       </c>
       <c r="Y63" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>11.452443814798121</v>
       </c>
       <c r="Z63" s="1">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="AE63" s="1"/>
       <c r="AF63" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="AG63" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH63" s="1"/>
@@ -8166,7 +8166,7 @@
         <v>100</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-8</v>
       </c>
       <c r="M64" s="1"/>
@@ -8178,7 +8178,7 @@
         <v>85</v>
       </c>
       <c r="Q64" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>18.399999999999999</v>
       </c>
       <c r="R64" s="5"/>
@@ -8187,7 +8187,7 @@
         <v>30</v>
       </c>
       <c r="T64" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="U64" s="5"/>
@@ -8196,11 +8196,11 @@
       </c>
       <c r="W64" s="1"/>
       <c r="X64" s="1">
-        <f>(F64+O64+P64+S64)/Q64</f>
+        <f t="shared" si="19"/>
         <v>16.847826086956523</v>
       </c>
       <c r="Y64" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>15.217391304347828</v>
       </c>
       <c r="Z64" s="1">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="AE64" s="1"/>
       <c r="AF64" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="AG64" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH64" s="1"/>
@@ -8283,7 +8283,7 @@
         <v>1093</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>39</v>
       </c>
       <c r="M65" s="1"/>
@@ -8295,19 +8295,19 @@
         <v>200</v>
       </c>
       <c r="Q65" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>226.4</v>
       </c>
       <c r="R65" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1215.5999999999999</v>
       </c>
       <c r="S65" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1216</v>
       </c>
       <c r="T65" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>501</v>
       </c>
       <c r="U65" s="5">
@@ -8317,11 +8317,11 @@
       <c r="V65" s="5"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1">
-        <f>(F65+O65+P65+S65)/Q65</f>
+        <f t="shared" si="19"/>
         <v>14.001766784452297</v>
       </c>
       <c r="Y65" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>8.6307420494699638</v>
       </c>
       <c r="Z65" s="1">
@@ -8343,11 +8343,11 @@
         <v>43</v>
       </c>
       <c r="AF65" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>205.41</v>
       </c>
       <c r="AG65" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>293.14999999999998</v>
       </c>
       <c r="AH65" s="1"/>
@@ -8402,7 +8402,7 @@
         <v>109</v>
       </c>
       <c r="L66" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-9</v>
       </c>
       <c r="M66" s="11"/>
@@ -8410,27 +8410,27 @@
       <c r="O66" s="11"/>
       <c r="P66" s="11"/>
       <c r="Q66" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>20</v>
       </c>
       <c r="R66" s="14"/>
       <c r="S66" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T66" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U66" s="5"/>
       <c r="V66" s="14"/>
       <c r="W66" s="11"/>
       <c r="X66" s="1">
-        <f>(F66+O66+P66+S66)/Q66</f>
+        <f t="shared" si="19"/>
         <v>119.1</v>
       </c>
       <c r="Y66" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>119.1</v>
       </c>
       <c r="Z66" s="11">
@@ -8450,11 +8450,11 @@
       </c>
       <c r="AE66" s="11"/>
       <c r="AF66" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG66" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH66" s="1"/>
@@ -8513,7 +8513,7 @@
         <v>295.7</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>79.977000000000032</v>
       </c>
       <c r="M67" s="1"/>
@@ -8525,11 +8525,11 @@
         <v>300</v>
       </c>
       <c r="Q67" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>75.135400000000004</v>
       </c>
       <c r="R67" s="5">
-        <f t="shared" ref="R67:R93" si="23">14*Q67-P67-O67-F67</f>
+        <f t="shared" ref="R67:R93" si="25">14*Q67-P67-O67-F67</f>
         <v>218.69160000000008</v>
       </c>
       <c r="S67" s="5">
@@ -8537,7 +8537,7 @@
         <v>240</v>
       </c>
       <c r="T67" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>99</v>
       </c>
       <c r="U67" s="5">
@@ -8549,11 +8549,11 @@
       </c>
       <c r="W67" s="1"/>
       <c r="X67" s="1">
-        <f>(F67+O67+P67+S67)/Q67</f>
+        <f t="shared" si="19"/>
         <v>14.283600007453209</v>
       </c>
       <c r="Y67" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>11.089366663383704</v>
       </c>
       <c r="Z67" s="1">
@@ -8573,11 +8573,11 @@
       </c>
       <c r="AE67" s="1"/>
       <c r="AF67" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>99</v>
       </c>
       <c r="AG67" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>141</v>
       </c>
       <c r="AH67" s="1"/>
@@ -8634,7 +8634,7 @@
         <v>56</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-6</v>
       </c>
       <c r="M68" s="1"/>
@@ -8646,30 +8646,30 @@
         <v>25</v>
       </c>
       <c r="Q68" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>10</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>35</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>35</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
       <c r="U68" s="5"/>
       <c r="V68" s="5"/>
       <c r="W68" s="1"/>
       <c r="X68" s="1">
-        <f>(F68+O68+P68+S68)/Q68</f>
+        <f t="shared" si="19"/>
         <v>14</v>
       </c>
       <c r="Y68" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>10.5</v>
       </c>
       <c r="Z68" s="1">
@@ -8689,11 +8689,11 @@
       </c>
       <c r="AE68" s="1"/>
       <c r="AF68" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.25</v>
       </c>
       <c r="AG68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH68" s="1"/>
@@ -8750,7 +8750,7 @@
         <v>763</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-106</v>
       </c>
       <c r="M69" s="1"/>
@@ -8762,33 +8762,33 @@
         <v>0</v>
       </c>
       <c r="Q69" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>131.4</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>540.60000000000014</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>541</v>
       </c>
       <c r="T69" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>223</v>
       </c>
       <c r="U69" s="5">
-        <f t="shared" ref="U69:U70" si="24">ROUND(S69/1.7,0)</f>
+        <f t="shared" ref="U69:U70" si="26">ROUND(S69/1.7,0)</f>
         <v>318</v>
       </c>
       <c r="V69" s="5"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1">
-        <f>(F69+O69+P69+S69)/Q69</f>
+        <f t="shared" si="19"/>
         <v>14.003044140030442</v>
       </c>
       <c r="Y69" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>9.8858447488584478</v>
       </c>
       <c r="Z69" s="1">
@@ -8810,11 +8810,11 @@
         <v>43</v>
       </c>
       <c r="AF69" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>91.429999999999993</v>
       </c>
       <c r="AG69" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>130.38</v>
       </c>
       <c r="AH69" s="1"/>
@@ -8869,7 +8869,7 @@
         <v>129.80000000000001</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L99" si="25">E70-K70</f>
+        <f t="shared" ref="L70:L99" si="27">E70-K70</f>
         <v>-3.7090000000000174</v>
       </c>
       <c r="M70" s="1"/>
@@ -8881,33 +8881,33 @@
         <v>60</v>
       </c>
       <c r="Q70" s="1">
-        <f t="shared" ref="Q70:Q99" si="26">E70/5</f>
+        <f t="shared" ref="Q70:Q99" si="28">E70/5</f>
         <v>25.2182</v>
       </c>
       <c r="R70" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>110.9658</v>
       </c>
       <c r="S70" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>111</v>
       </c>
       <c r="T70" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46</v>
       </c>
       <c r="U70" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>65</v>
       </c>
       <c r="V70" s="5"/>
       <c r="W70" s="1"/>
       <c r="X70" s="1">
-        <f>(F70+O70+P70+S70)/Q70</f>
+        <f t="shared" si="19"/>
         <v>14.001356163405795</v>
       </c>
       <c r="Y70" s="1">
-        <f t="shared" ref="Y70:Y99" si="27">(F70+O70+P70)/Q70</f>
+        <f t="shared" ref="Y70:Y99" si="29">(F70+O70+P70)/Q70</f>
         <v>9.599773179687686</v>
       </c>
       <c r="Z70" s="1">
@@ -8927,11 +8927,11 @@
       </c>
       <c r="AE70" s="1"/>
       <c r="AF70" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>46</v>
       </c>
       <c r="AG70" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>65</v>
       </c>
       <c r="AH70" s="1"/>
@@ -8984,7 +8984,7 @@
         <v>173</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-158</v>
       </c>
       <c r="M71" s="1"/>
@@ -8996,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="Q71" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3</v>
       </c>
       <c r="R71" s="5">
@@ -9004,22 +9004,22 @@
         <v>27</v>
       </c>
       <c r="S71" s="5">
-        <f t="shared" ref="S71:S97" si="28">ROUND(R71,0)</f>
+        <f t="shared" ref="S71:S97" si="30">ROUND(R71,0)</f>
         <v>27</v>
       </c>
       <c r="T71" s="5">
-        <f t="shared" ref="T71:T99" si="29">ROUND(S71-U71,0)</f>
+        <f t="shared" ref="T71:T97" si="31">ROUND(S71-U71,0)</f>
         <v>27</v>
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="5"/>
       <c r="W71" s="1"/>
       <c r="X71" s="1">
-        <f t="shared" ref="X71:X99" si="30">(F71+O71+P71+S71)/Q71</f>
+        <f t="shared" ref="X71:X99" si="32">(F71+O71+P71+S71)/Q71</f>
         <v>9</v>
       </c>
       <c r="Y71" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Z71" s="1">
@@ -9039,11 +9039,11 @@
       </c>
       <c r="AE71" s="1"/>
       <c r="AF71" s="1">
-        <f t="shared" ref="AF71:AF99" si="31">G71*T71</f>
+        <f t="shared" ref="AF71:AF99" si="33">G71*T71</f>
         <v>8.1</v>
       </c>
       <c r="AG71" s="1">
-        <f t="shared" ref="AG71:AG99" si="32">G71*U71</f>
+        <f t="shared" ref="AG71:AG99" si="34">G71*U71</f>
         <v>0</v>
       </c>
       <c r="AH71" s="1"/>
@@ -9100,7 +9100,7 @@
         <v>215</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-9</v>
       </c>
       <c r="M72" s="1"/>
@@ -9112,19 +9112,19 @@
         <v>0</v>
       </c>
       <c r="Q72" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>41.2</v>
       </c>
       <c r="R72" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>221.80000000000007</v>
       </c>
       <c r="S72" s="5">
-        <f t="shared" ref="S72:S73" si="33">V72</f>
+        <f t="shared" ref="S72:S73" si="35">V72</f>
         <v>250</v>
       </c>
       <c r="T72" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>103</v>
       </c>
       <c r="U72" s="5">
@@ -9136,11 +9136,11 @@
       </c>
       <c r="W72" s="1"/>
       <c r="X72" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.684466019417474</v>
       </c>
       <c r="Y72" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8.616504854368932</v>
       </c>
       <c r="Z72" s="1">
@@ -9162,11 +9162,11 @@
         <v>43</v>
       </c>
       <c r="AF72" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>18.54</v>
       </c>
       <c r="AG72" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>26.459999999999997</v>
       </c>
       <c r="AH72" s="1"/>
@@ -9221,7 +9221,7 @@
         <v>10</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="M73" s="1"/>
@@ -9233,16 +9233,16 @@
         <v>12</v>
       </c>
       <c r="Q73" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.8</v>
       </c>
       <c r="R73" s="5"/>
       <c r="S73" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="T73" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>30</v>
       </c>
       <c r="U73" s="5"/>
@@ -9251,11 +9251,11 @@
       </c>
       <c r="W73" s="1"/>
       <c r="X73" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>31.666666666666664</v>
       </c>
       <c r="Y73" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>15</v>
       </c>
       <c r="Z73" s="1">
@@ -9275,11 +9275,11 @@
       </c>
       <c r="AE73" s="1"/>
       <c r="AF73" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>6.6</v>
       </c>
       <c r="AG73" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH73" s="1"/>
@@ -9336,7 +9336,7 @@
         <v>820.8</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-71.799999999999955</v>
       </c>
       <c r="M74" s="1"/>
@@ -9348,33 +9348,33 @@
         <v>600</v>
       </c>
       <c r="Q74" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>149.80000000000001</v>
       </c>
       <c r="R74" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>520.20000000000027</v>
       </c>
       <c r="S74" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>520</v>
       </c>
       <c r="T74" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>214</v>
       </c>
       <c r="U74" s="5">
-        <f t="shared" ref="U74:U75" si="34">ROUND(S74/1.7,0)</f>
+        <f t="shared" ref="U74:U75" si="36">ROUND(S74/1.7,0)</f>
         <v>306</v>
       </c>
       <c r="V74" s="5"/>
       <c r="W74" s="1"/>
       <c r="X74" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>13.998664886515353</v>
       </c>
       <c r="Y74" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>10.527369826435246</v>
       </c>
       <c r="Z74" s="1">
@@ -9396,11 +9396,11 @@
         <v>33</v>
       </c>
       <c r="AF74" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>74.899999999999991</v>
       </c>
       <c r="AG74" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>107.1</v>
       </c>
       <c r="AH74" s="1"/>
@@ -9457,7 +9457,7 @@
         <v>107.8</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2.0880000000000081</v>
       </c>
       <c r="M75" s="1"/>
@@ -9469,33 +9469,33 @@
         <v>60</v>
       </c>
       <c r="Q75" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>21.977600000000002</v>
       </c>
       <c r="R75" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>106.92740000000005</v>
       </c>
       <c r="S75" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>107</v>
       </c>
       <c r="T75" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>44</v>
       </c>
       <c r="U75" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>63</v>
       </c>
       <c r="V75" s="5"/>
       <c r="W75" s="1"/>
       <c r="X75" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.003303363424576</v>
       </c>
       <c r="Y75" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9.1347098864298193</v>
       </c>
       <c r="Z75" s="1">
@@ -9515,11 +9515,11 @@
       </c>
       <c r="AE75" s="1"/>
       <c r="AF75" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>44</v>
       </c>
       <c r="AG75" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>63</v>
       </c>
       <c r="AH75" s="1"/>
@@ -9570,7 +9570,7 @@
         <v>3.2</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-3.2</v>
       </c>
       <c r="M76" s="1"/>
@@ -9582,27 +9582,27 @@
         <v>0</v>
       </c>
       <c r="Q76" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="R76" s="5"/>
       <c r="S76" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="T76" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="U76" s="5"/>
       <c r="V76" s="5"/>
       <c r="W76" s="1"/>
       <c r="X76" s="1" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y76" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z76" s="1">
@@ -9622,11 +9622,11 @@
       </c>
       <c r="AE76" s="1"/>
       <c r="AF76" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG76" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH76" s="1"/>
@@ -9683,7 +9683,7 @@
         <v>262.3</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2.6419999999999959</v>
       </c>
       <c r="M77" s="1"/>
@@ -9695,23 +9695,23 @@
         <v>110</v>
       </c>
       <c r="Q77" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>52.988399999999999</v>
       </c>
       <c r="R77" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>202.08359999999993</v>
       </c>
       <c r="S77" s="5">
-        <f t="shared" ref="S77:S78" si="35">V77</f>
+        <f t="shared" ref="S77:S78" si="37">V77</f>
         <v>230</v>
       </c>
       <c r="T77" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>95</v>
       </c>
       <c r="U77" s="5">
-        <f t="shared" ref="U77:U79" si="36">ROUND(S77/1.7,0)</f>
+        <f t="shared" ref="U77:U79" si="38">ROUND(S77/1.7,0)</f>
         <v>135</v>
       </c>
       <c r="V77" s="5">
@@ -9719,11 +9719,11 @@
       </c>
       <c r="W77" s="1"/>
       <c r="X77" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.526839836643493</v>
       </c>
       <c r="Y77" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>10.186267183006093</v>
       </c>
       <c r="Z77" s="1">
@@ -9743,11 +9743,11 @@
       </c>
       <c r="AE77" s="1"/>
       <c r="AF77" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>95</v>
       </c>
       <c r="AG77" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>135</v>
       </c>
       <c r="AH77" s="1"/>
@@ -9804,7 +9804,7 @@
         <v>876.4</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-174.99099999999999</v>
       </c>
       <c r="M78" s="1"/>
@@ -9816,23 +9816,23 @@
         <v>400</v>
       </c>
       <c r="Q78" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>140.2818</v>
       </c>
       <c r="R78" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>216.35420000000011</v>
       </c>
       <c r="S78" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>240</v>
       </c>
       <c r="T78" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>99</v>
       </c>
       <c r="U78" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>141</v>
       </c>
       <c r="V78" s="5">
@@ -9840,11 +9840,11 @@
       </c>
       <c r="W78" s="1"/>
       <c r="X78" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.168559285666422</v>
       </c>
       <c r="Y78" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>12.457717251988496</v>
       </c>
       <c r="Z78" s="1">
@@ -9864,11 +9864,11 @@
       </c>
       <c r="AE78" s="1"/>
       <c r="AF78" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>34.65</v>
       </c>
       <c r="AG78" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>49.349999999999994</v>
       </c>
       <c r="AH78" s="1"/>
@@ -9925,7 +9925,7 @@
         <v>116</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-13</v>
       </c>
       <c r="M79" s="1"/>
@@ -9937,7 +9937,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>20.6</v>
       </c>
       <c r="R79" s="5">
@@ -9945,25 +9945,25 @@
         <v>188.4</v>
       </c>
       <c r="S79" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>188</v>
       </c>
       <c r="T79" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>77</v>
       </c>
       <c r="U79" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>111</v>
       </c>
       <c r="V79" s="5"/>
       <c r="W79" s="1"/>
       <c r="X79" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8.9805825242718438</v>
       </c>
       <c r="Y79" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-0.14563106796116504</v>
       </c>
       <c r="Z79" s="1">
@@ -9983,11 +9983,11 @@
       </c>
       <c r="AE79" s="1"/>
       <c r="AF79" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>23.099999999999998</v>
       </c>
       <c r="AG79" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>33.299999999999997</v>
       </c>
       <c r="AH79" s="1"/>
@@ -10044,7 +10044,7 @@
         <v>85</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-14</v>
       </c>
       <c r="M80" s="1"/>
@@ -10056,30 +10056,30 @@
         <v>50</v>
       </c>
       <c r="Q80" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>14.2</v>
       </c>
       <c r="R80" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>56.799999999999983</v>
       </c>
       <c r="S80" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>57</v>
       </c>
       <c r="T80" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>57</v>
       </c>
       <c r="U80" s="5"/>
       <c r="V80" s="5"/>
       <c r="W80" s="1"/>
       <c r="X80" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.014084507042254</v>
       </c>
       <c r="Y80" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>10</v>
       </c>
       <c r="Z80" s="1">
@@ -10099,11 +10099,11 @@
       </c>
       <c r="AE80" s="1"/>
       <c r="AF80" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>17.099999999999998</v>
       </c>
       <c r="AG80" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH80" s="1"/>
@@ -10160,7 +10160,7 @@
         <v>134</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-8</v>
       </c>
       <c r="M81" s="1"/>
@@ -10172,19 +10172,19 @@
         <v>0</v>
       </c>
       <c r="Q81" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>25.2</v>
       </c>
       <c r="R81" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>120.80000000000001</v>
       </c>
       <c r="S81" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>121</v>
       </c>
       <c r="T81" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>50</v>
       </c>
       <c r="U81" s="5">
@@ -10194,11 +10194,11 @@
       <c r="V81" s="5"/>
       <c r="W81" s="1"/>
       <c r="X81" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.007936507936508</v>
       </c>
       <c r="Y81" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9.2063492063492074</v>
       </c>
       <c r="Z81" s="1">
@@ -10220,11 +10220,11 @@
         <v>43</v>
       </c>
       <c r="AF81" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>14.000000000000002</v>
       </c>
       <c r="AG81" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>19.880000000000003</v>
       </c>
       <c r="AH81" s="1"/>
@@ -10281,7 +10281,7 @@
         <v>400</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-358</v>
       </c>
       <c r="M82" s="1"/>
@@ -10293,27 +10293,27 @@
         <v>330</v>
       </c>
       <c r="Q82" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>8.4</v>
       </c>
       <c r="R82" s="5"/>
       <c r="S82" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="T82" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="U82" s="5"/>
       <c r="V82" s="5"/>
       <c r="W82" s="1"/>
       <c r="X82" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>91.904761904761898</v>
       </c>
       <c r="Y82" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>91.904761904761898</v>
       </c>
       <c r="Z82" s="1">
@@ -10335,11 +10335,11 @@
         <v>111</v>
       </c>
       <c r="AF82" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG82" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH82" s="1"/>
@@ -10396,7 +10396,7 @@
         <v>54</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-8</v>
       </c>
       <c r="M83" s="1"/>
@@ -10408,29 +10408,29 @@
         <v>0</v>
       </c>
       <c r="Q83" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="R83" s="5">
         <v>8</v>
       </c>
       <c r="S83" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="T83" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>8</v>
       </c>
       <c r="U83" s="5"/>
       <c r="V83" s="5"/>
       <c r="W83" s="1"/>
       <c r="X83" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.456521739130435</v>
       </c>
       <c r="Y83" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>13.586956521739131</v>
       </c>
       <c r="Z83" s="1">
@@ -10450,11 +10450,11 @@
       </c>
       <c r="AE83" s="1"/>
       <c r="AF83" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2.2400000000000002</v>
       </c>
       <c r="AG83" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH83" s="1"/>
@@ -10511,7 +10511,7 @@
         <v>205</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-88</v>
       </c>
       <c r="M84" s="1"/>
@@ -10523,27 +10523,27 @@
         <v>150</v>
       </c>
       <c r="Q84" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>23.4</v>
       </c>
       <c r="R84" s="5"/>
       <c r="S84" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="T84" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="U84" s="5"/>
       <c r="V84" s="5"/>
       <c r="W84" s="1"/>
       <c r="X84" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>25.982905982905983</v>
       </c>
       <c r="Y84" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>25.982905982905983</v>
       </c>
       <c r="Z84" s="1">
@@ -10565,11 +10565,11 @@
         <v>111</v>
       </c>
       <c r="AF84" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG84" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH84" s="1"/>
@@ -10626,7 +10626,7 @@
         <v>421</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-79</v>
       </c>
       <c r="M85" s="1"/>
@@ -10638,11 +10638,11 @@
         <v>420</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>68.400000000000006</v>
       </c>
       <c r="R85" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>119.60000000000014</v>
       </c>
       <c r="S85" s="5">
@@ -10650,7 +10650,7 @@
         <v>140</v>
       </c>
       <c r="T85" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>58</v>
       </c>
       <c r="U85" s="5">
@@ -10662,11 +10662,11 @@
       </c>
       <c r="W85" s="1"/>
       <c r="X85" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.298245614035087</v>
       </c>
       <c r="Y85" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>12.251461988304092</v>
       </c>
       <c r="Z85" s="1">
@@ -10686,11 +10686,11 @@
       </c>
       <c r="AE85" s="1"/>
       <c r="AF85" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>23.200000000000003</v>
       </c>
       <c r="AG85" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>32.800000000000004</v>
       </c>
       <c r="AH85" s="1"/>
@@ -10745,7 +10745,7 @@
         <v>13</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-4</v>
       </c>
       <c r="M86" s="1"/>
@@ -10757,27 +10757,27 @@
         <v>0</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.8</v>
       </c>
       <c r="R86" s="5"/>
       <c r="S86" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="T86" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="U86" s="5"/>
       <c r="V86" s="5"/>
       <c r="W86" s="1"/>
       <c r="X86" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>86.666666666666671</v>
       </c>
       <c r="Y86" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>86.666666666666671</v>
       </c>
       <c r="Z86" s="1">
@@ -10799,11 +10799,11 @@
         <v>91</v>
       </c>
       <c r="AF86" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG86" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH86" s="1"/>
@@ -10860,7 +10860,7 @@
         <v>29</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-12</v>
       </c>
       <c r="M87" s="1"/>
@@ -10872,7 +10872,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3.4</v>
       </c>
       <c r="R87" s="5">
@@ -10880,22 +10880,22 @@
         <v>32.199999999999996</v>
       </c>
       <c r="S87" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>32</v>
       </c>
       <c r="T87" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>32</v>
       </c>
       <c r="U87" s="5"/>
       <c r="V87" s="5"/>
       <c r="W87" s="1"/>
       <c r="X87" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>12.941176470588236</v>
       </c>
       <c r="Y87" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>3.5294117647058822</v>
       </c>
       <c r="Z87" s="1">
@@ -10915,11 +10915,11 @@
       </c>
       <c r="AE87" s="1"/>
       <c r="AF87" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>10.56</v>
       </c>
       <c r="AG87" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH87" s="1"/>
@@ -10976,7 +10976,7 @@
         <v>79</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-30</v>
       </c>
       <c r="M88" s="1"/>
@@ -10988,7 +10988,7 @@
         <v>70</v>
       </c>
       <c r="Q88" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="R88" s="5"/>
@@ -10997,7 +10997,7 @@
         <v>30</v>
       </c>
       <c r="T88" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>30</v>
       </c>
       <c r="U88" s="5"/>
@@ -11006,11 +11006,11 @@
       </c>
       <c r="W88" s="1"/>
       <c r="X88" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>17.857142857142854</v>
       </c>
       <c r="Y88" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>14.795918367346937</v>
       </c>
       <c r="Z88" s="1">
@@ -11030,11 +11030,11 @@
       </c>
       <c r="AE88" s="1"/>
       <c r="AF88" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3</v>
       </c>
       <c r="AG88" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH88" s="1"/>
@@ -11091,7 +11091,7 @@
         <v>18</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-4</v>
       </c>
       <c r="M89" s="1"/>
@@ -11103,30 +11103,30 @@
         <v>0</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>2.8</v>
       </c>
       <c r="R89" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10.199999999999996</v>
       </c>
       <c r="S89" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>10</v>
       </c>
       <c r="T89" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="U89" s="5"/>
       <c r="V89" s="5"/>
       <c r="W89" s="1"/>
       <c r="X89" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>13.928571428571429</v>
       </c>
       <c r="Y89" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>10.357142857142858</v>
       </c>
       <c r="Z89" s="1">
@@ -11146,11 +11146,11 @@
       </c>
       <c r="AE89" s="1"/>
       <c r="AF89" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="AG89" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH89" s="1"/>
@@ -11207,7 +11207,7 @@
         <v>20</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-5</v>
       </c>
       <c r="M90" s="1"/>
@@ -11219,30 +11219,30 @@
         <v>0</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3</v>
       </c>
       <c r="R90" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>16</v>
       </c>
       <c r="S90" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>16</v>
       </c>
       <c r="T90" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>16</v>
       </c>
       <c r="U90" s="5"/>
       <c r="V90" s="5"/>
       <c r="W90" s="1"/>
       <c r="X90" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14</v>
       </c>
       <c r="Y90" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8.6666666666666661</v>
       </c>
       <c r="Z90" s="1">
@@ -11262,11 +11262,11 @@
       </c>
       <c r="AE90" s="1"/>
       <c r="AF90" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>4.4800000000000004</v>
       </c>
       <c r="AG90" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH90" s="1"/>
@@ -11321,7 +11321,7 @@
         <v>179</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-13</v>
       </c>
       <c r="M91" s="1"/>
@@ -11333,19 +11333,19 @@
         <v>90</v>
       </c>
       <c r="Q91" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>33.200000000000003</v>
       </c>
       <c r="R91" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>312.80000000000007</v>
       </c>
       <c r="S91" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>313</v>
       </c>
       <c r="T91" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>129</v>
       </c>
       <c r="U91" s="5">
@@ -11355,11 +11355,11 @@
       <c r="V91" s="5"/>
       <c r="W91" s="1"/>
       <c r="X91" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.006024096385541</v>
       </c>
       <c r="Y91" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>4.5783132530120474</v>
       </c>
       <c r="Z91" s="1">
@@ -11379,11 +11379,11 @@
       </c>
       <c r="AE91" s="1"/>
       <c r="AF91" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>38.699999999999996</v>
       </c>
       <c r="AG91" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>55.199999999999996</v>
       </c>
       <c r="AH91" s="1"/>
@@ -11440,7 +11440,7 @@
         <v>164</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-9</v>
       </c>
       <c r="M92" s="1"/>
@@ -11452,16 +11452,16 @@
         <v>140</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="R92" s="5"/>
       <c r="S92" s="5">
-        <f t="shared" ref="S92:S93" si="37">V92</f>
+        <f t="shared" ref="S92:S93" si="39">V92</f>
         <v>700</v>
       </c>
       <c r="T92" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>700</v>
       </c>
       <c r="U92" s="5"/>
@@ -11472,11 +11472,11 @@
         <v>140</v>
       </c>
       <c r="X92" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>38.12903225806452</v>
       </c>
       <c r="Y92" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>15.548387096774194</v>
       </c>
       <c r="Z92" s="1">
@@ -11496,11 +11496,11 @@
       </c>
       <c r="AE92" s="1"/>
       <c r="AF92" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>84</v>
       </c>
       <c r="AG92" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH92" s="1"/>
@@ -11555,7 +11555,7 @@
         <v>218</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-32</v>
       </c>
       <c r="M93" s="1"/>
@@ -11567,19 +11567,19 @@
         <v>200</v>
       </c>
       <c r="Q93" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37.200000000000003</v>
       </c>
       <c r="R93" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>22.800000000000068</v>
       </c>
       <c r="S93" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>60</v>
       </c>
       <c r="T93" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>60</v>
       </c>
       <c r="U93" s="5"/>
@@ -11588,11 +11588,11 @@
       </c>
       <c r="W93" s="1"/>
       <c r="X93" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.999999999999998</v>
       </c>
       <c r="Y93" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>13.387096774193548</v>
       </c>
       <c r="Z93" s="1">
@@ -11612,11 +11612,11 @@
       </c>
       <c r="AE93" s="1"/>
       <c r="AF93" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>19.8</v>
       </c>
       <c r="AG93" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH93" s="1"/>
@@ -11665,7 +11665,7 @@
         <v>193</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-37</v>
       </c>
       <c r="M94" s="1"/>
@@ -11673,7 +11673,7 @@
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
       <c r="Q94" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>31.2</v>
       </c>
       <c r="R94" s="5">
@@ -11681,11 +11681,11 @@
         <v>280.8</v>
       </c>
       <c r="S94" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>281</v>
       </c>
       <c r="T94" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>116</v>
       </c>
       <c r="U94" s="5">
@@ -11695,11 +11695,11 @@
       <c r="V94" s="5"/>
       <c r="W94" s="1"/>
       <c r="X94" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>9.0064102564102573</v>
       </c>
       <c r="Y94" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Z94" s="1">
@@ -11719,11 +11719,11 @@
       </c>
       <c r="AE94" s="1"/>
       <c r="AF94" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32.480000000000004</v>
       </c>
       <c r="AG94" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>46.2</v>
       </c>
       <c r="AH94" s="1"/>
@@ -11776,7 +11776,7 @@
         <v>181</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-134</v>
       </c>
       <c r="M95" s="1"/>
@@ -11788,7 +11788,7 @@
         <v>200</v>
       </c>
       <c r="Q95" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>9.4</v>
       </c>
       <c r="R95" s="5"/>
@@ -11797,7 +11797,7 @@
         <v>40</v>
       </c>
       <c r="T95" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>40</v>
       </c>
       <c r="U95" s="5"/>
@@ -11806,11 +11806,11 @@
       </c>
       <c r="W95" s="1"/>
       <c r="X95" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46.914893617021278</v>
       </c>
       <c r="Y95" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>42.659574468085104</v>
       </c>
       <c r="Z95" s="1">
@@ -11830,11 +11830,11 @@
       </c>
       <c r="AE95" s="1"/>
       <c r="AF95" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>16</v>
       </c>
       <c r="AG95" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH95" s="1"/>
@@ -11890,7 +11890,7 @@
         <v>14.5</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-6.0370000000000008</v>
       </c>
       <c r="M96" s="1"/>
@@ -11902,7 +11902,7 @@
         <v>0</v>
       </c>
       <c r="Q96" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.6925999999999999</v>
       </c>
       <c r="R96" s="5">
@@ -11910,22 +11910,22 @@
         <v>14.450599999999998</v>
       </c>
       <c r="S96" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>14</v>
       </c>
       <c r="T96" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>14</v>
       </c>
       <c r="U96" s="5"/>
       <c r="V96" s="5"/>
       <c r="W96" s="1"/>
       <c r="X96" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10.733782346685572</v>
       </c>
       <c r="Y96" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.4624837528063339</v>
       </c>
       <c r="Z96" s="1">
@@ -11947,11 +11947,11 @@
         <v>135</v>
       </c>
       <c r="AF96" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>14</v>
       </c>
       <c r="AG96" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH96" s="1"/>
@@ -12004,7 +12004,7 @@
         <v>18</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>56</v>
       </c>
       <c r="M97" s="1"/>
@@ -12012,7 +12012,7 @@
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
       <c r="Q97" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>14.8</v>
       </c>
       <c r="R97" s="5">
@@ -12020,11 +12020,11 @@
         <v>126</v>
       </c>
       <c r="S97" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>126</v>
       </c>
       <c r="T97" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>52</v>
       </c>
       <c r="U97" s="5">
@@ -12034,11 +12034,11 @@
       <c r="V97" s="5"/>
       <c r="W97" s="1"/>
       <c r="X97" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10</v>
       </c>
       <c r="Y97" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.4864864864864864</v>
       </c>
       <c r="Z97" s="1">
@@ -12060,11 +12060,11 @@
         <v>136</v>
       </c>
       <c r="AF97" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>17.16</v>
       </c>
       <c r="AG97" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>24.42</v>
       </c>
       <c r="AH97" s="1"/>
@@ -12123,7 +12123,7 @@
         <v>85</v>
       </c>
       <c r="L98" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-44</v>
       </c>
       <c r="M98" s="11"/>
@@ -12135,29 +12135,23 @@
         <v>0</v>
       </c>
       <c r="Q98" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="R98" s="14"/>
-      <c r="S98" s="5">
-        <f t="shared" ref="S98:S99" si="38">V98</f>
-        <v>40</v>
-      </c>
-      <c r="T98" s="5">
-        <f t="shared" si="29"/>
-        <v>40</v>
-      </c>
+      <c r="S98" s="5"/>
+      <c r="T98" s="5"/>
       <c r="U98" s="5"/>
       <c r="V98" s="14">
         <v>40</v>
       </c>
       <c r="W98" s="11"/>
       <c r="X98" s="1">
-        <f t="shared" si="30"/>
-        <v>1.5853658536585367</v>
+        <f t="shared" si="32"/>
+        <v>-3.2926829268292686</v>
       </c>
       <c r="Y98" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-3.2926829268292686</v>
       </c>
       <c r="Z98" s="11">
@@ -12177,11 +12171,11 @@
       </c>
       <c r="AE98" s="11"/>
       <c r="AF98" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG98" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH98" s="1"/>
@@ -12240,7 +12234,7 @@
         <v>89.447999999999993</v>
       </c>
       <c r="L99" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-10.889999999999986</v>
       </c>
       <c r="M99" s="11"/>
@@ -12252,32 +12246,23 @@
         <v>0</v>
       </c>
       <c r="Q99" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>15.711600000000001</v>
       </c>
       <c r="R99" s="14"/>
-      <c r="S99" s="5">
-        <f t="shared" si="38"/>
-        <v>150</v>
-      </c>
-      <c r="T99" s="5">
-        <f t="shared" si="29"/>
-        <v>62</v>
-      </c>
-      <c r="U99" s="5">
-        <f>ROUND(S99/1.7,0)</f>
-        <v>88</v>
-      </c>
+      <c r="S99" s="5"/>
+      <c r="T99" s="5"/>
+      <c r="U99" s="5"/>
       <c r="V99" s="14">
         <v>150</v>
       </c>
       <c r="W99" s="11"/>
       <c r="X99" s="1">
-        <f t="shared" si="30"/>
-        <v>-0.61495964764887123</v>
+        <f t="shared" si="32"/>
+        <v>-10.162045876931694</v>
       </c>
       <c r="Y99" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-10.162045876931694</v>
       </c>
       <c r="Z99" s="11">
@@ -12297,11 +12282,11 @@
       </c>
       <c r="AE99" s="11"/>
       <c r="AF99" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG99" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH99" s="1"/>
